--- a/results/Int All Data -0.5/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.5/Rando_9_permute.xlsx
@@ -440,797 +440,797 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8501071211242857</v>
+        <v>0.8395905272519741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8501071211242857</v>
+        <v>0.8411566560925814</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8533529812078942</v>
+        <v>0.8449735887917098</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8551158888532819</v>
+        <v>0.8410734796901949</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8566404294926959</v>
+        <v>0.8466533200347108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8570867375046359</v>
+        <v>0.8460102332179906</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8508110599410204</v>
+        <v>0.8460934096203772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8512573679529603</v>
+        <v>0.8460934096203772</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8550022864508882</v>
+        <v>0.8466949082359041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8539544798234211</v>
+        <v>0.8450040147917169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8558837402735819</v>
+        <v>0.8435210623534961</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8532170544031283</v>
+        <v>0.8436458269570759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8489954018932533</v>
+        <v>0.8402752022698876</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8408016260806631</v>
+        <v>0.8409598772878011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8410399930866367</v>
+        <v>0.8484192882836495</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8399617604591625</v>
+        <v>0.8493646547099087</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8406464354770761</v>
+        <v>0.8490431113015486</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8486130064848788</v>
+        <v>0.8490015231003554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8416557145069008</v>
+        <v>0.8516986349708162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.841084641891381</v>
+        <v>0.8432279645546101</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8438649301642284</v>
+        <v>0.8425848777378899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8461461600227564</v>
+        <v>0.841226689903249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8418636555128671</v>
+        <v>0.8455812086143387</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8447575461881083</v>
+        <v>0.841983379122363</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8424235659272008</v>
+        <v>0.848195144082413</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8417804791104806</v>
+        <v>0.8487550544967468</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8386035726245216</v>
+        <v>0.8497196847218271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.836696636576733</v>
+        <v>0.8443285215844565</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8371733705886801</v>
+        <v>0.8458530622238705</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8411150678913881</v>
+        <v>0.8550642186639206</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8480257306740889</v>
+        <v>0.8621442948549454</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8651922959207556</v>
+        <v>0.8537872268411331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8608986292096802</v>
+        <v>0.859219978179697</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8674319375780903</v>
+        <v>0.8597991523928519</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8429834763415346</v>
+        <v>0.839572343666171</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.843221843347508</v>
+        <v>0.8337237103156743</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8057422323682231</v>
+        <v>0.8395307554649777</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8126417329497377</v>
+        <v>0.8269439333436553</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8150061392106523</v>
+        <v>0.8170927506904362</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.818448778099041</v>
+        <v>0.824765143686335</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8093816500613922</v>
+        <v>0.8234789700528944</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8050768211491306</v>
+        <v>0.8191548773418118</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8042176917288089</v>
+        <v>0.8045891049715004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.807100420202864</v>
+        <v>0.81663528047731</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8064573333861438</v>
+        <v>0.8136693756008685</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8133760977664796</v>
+        <v>0.8134310085948949</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8135008623700594</v>
+        <v>0.8311655858535303</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7567479106879876</v>
+        <v>0.8236788094612257</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7716748342773194</v>
+        <v>0.8228389438397252</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7710733356617925</v>
+        <v>0.8147810948319009</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7594561847596346</v>
+        <v>0.8189388347382104</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8115685413163476</v>
+        <v>0.8247539814851488</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.822512179401778</v>
+        <v>0.8244020120767815</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8208628741587841</v>
+        <v>0.8358193235706082</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8143904177903882</v>
+        <v>0.8346579145407474</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8073468888064727</v>
+        <v>0.831120937048786</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8091513846530536</v>
+        <v>0.8314008922559528</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8128658771509742</v>
+        <v>0.8407794817137939</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8135089639676945</v>
+        <v>0.8385398400564592</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.816777148453675</v>
+        <v>0.8434350053830615</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.816777148453675</v>
+        <v>0.8610448180381172</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8135728765712599</v>
+        <v>0.8541788040601607</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8129937023581051</v>
+        <v>0.8488403913251694</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8157324024297592</v>
+        <v>0.8552154484864416</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8095845500732745</v>
+        <v>0.8515537063909002</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8095845500732745</v>
+        <v>0.8498739751478992</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6599410203692169</v>
+        <v>0.8438782527914505</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6298183801845725</v>
+        <v>0.8407571573114219</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6224644699934827</v>
+        <v>0.8407571573114219</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6007851348285882</v>
+        <v>0.8310611652617896</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6062290483683382</v>
+        <v>0.8358924179848266</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6062290483683382</v>
+        <v>0.8366906954051339</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5966131721175416</v>
+        <v>0.8340240095346803</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5969347155259017</v>
+        <v>0.8321444388833478</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5969347155259017</v>
+        <v>0.8452222178213544</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6227525267982846</v>
+        <v>0.8448509846141659</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6286234845511536</v>
+        <v>0.8414387717257843</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6286234845511536</v>
+        <v>0.8524706272076854</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6574903771023646</v>
+        <v>0.8482216093013542</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6568472902856444</v>
+        <v>0.8502452083550875</v>
       </c>
     </row>
     <row r="82">
@@ -1240,613 +1240,613 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6775346298290023</v>
+        <v>0.8527597642255054</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6325986684574199</v>
+        <v>0.8536797456458414</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6445515855726749</v>
+        <v>0.8559690771020045</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6445515855726749</v>
+        <v>0.8550460350781175</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6445515855726749</v>
+        <v>0.8544861246637837</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5899388959502814</v>
+        <v>0.8520304404028474</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5968079705317889</v>
+        <v>0.8513041771837406</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6123333321330966</v>
+        <v>0.8398676018910929</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6125716991390702</v>
+        <v>0.8066168448418027</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5727399243130745</v>
+        <v>0.8059849202262686</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5585900339546959</v>
+        <v>0.8097379403218314</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5588811513630488</v>
+        <v>0.8236829502777948</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5507979173493013</v>
+        <v>0.8221695718395667</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5526440013970755</v>
+        <v>0.8234750092718284</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5400764430745744</v>
+        <v>0.8216289252240543</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5140182844056848</v>
+        <v>0.8216289252240543</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5140182844056848</v>
+        <v>0.8234719486682773</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5042776435513083</v>
+        <v>0.8234719486682773</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5037177331369745</v>
+        <v>0.7809988729777513</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5177459194953244</v>
+        <v>0.6579561289486286</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5177459194953244</v>
+        <v>0.6576345855402685</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5294979169892303</v>
+        <v>0.6618369742513224</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5317568224453862</v>
+        <v>0.635518124174087</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5225760920053435</v>
+        <v>0.6486232685085499</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5225760920053435</v>
+        <v>0.6201803595669066</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5089018554458939</v>
+        <v>0.5812278781375687</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5037652625097669</v>
+        <v>0.5729224803131178</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5042947469240935</v>
+        <v>0.5732024355202846</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.503920453113354</v>
+        <v>0.5960928695138681</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4992109043903458</v>
+        <v>0.5905018669681661</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5016970146512892</v>
+        <v>0.5899947069562118</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4999675936094598</v>
+        <v>0.584282000410481</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4963890279163051</v>
+        <v>0.5834837229901737</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5010650900357551</v>
+        <v>0.5309140762558376</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5051781811373203</v>
+        <v>0.5309140762558376</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5051781811373203</v>
+        <v>0.5326242334988459</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.507398558995834</v>
+        <v>0.5287576110008894</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4999695739999928</v>
+        <v>0.5170137151046186</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5004878962131333</v>
+        <v>0.5167753480986451</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5004878962131333</v>
+        <v>0.5191620787619318</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4999695739999928</v>
+        <v>0.5147051198496343</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5001247646035798</v>
+        <v>0.5049826625810609</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5001247646035798</v>
+        <v>0.5210394889872283</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5001247646035798</v>
+        <v>0.5182592007143809</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5001247646035798</v>
+        <v>0.5008733522250588</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5001247646035798</v>
+        <v>0.5011533074322256</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4991601343784994</v>
+        <v>0.4982817411593566</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4961638035020506</v>
+        <v>0.4998143833964058</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.497283624330718</v>
+        <v>0.4966932879163771</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4985282097629652</v>
+        <v>0.4941848532530615</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4985282097629652</v>
+        <v>0.4941848532530615</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4979682993486315</v>
+        <v>0.493500178235148</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4971700219283243</v>
+        <v>0.4970148313247372</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.495925436496077</v>
+        <v>0.4964549209104036</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.495925436496077</v>
+        <v>0.4964549209104036</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4983618569581921</v>
+        <v>0.4964549209104036</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4994400895856663</v>
+        <v>0.4964549209104036</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4994400895856663</v>
+        <v>0.5000831764023865</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5003631316095534</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.5003631316095534</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5003631316095534</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1856,7 +1856,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1866,7 +1866,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
